--- a/import/schedule/Корректировки/01.09.xlsx
+++ b/import/schedule/Корректировки/01.09.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50446AF3-570E-4189-A3F3-8E6AAD9D0551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="6840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -564,7 +565,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -901,6 +902,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -925,26 +946,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1038,6 +1039,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1073,6 +1091,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1248,7 +1283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G185"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1262,37 +1297,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -1304,26 +1339,26 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="25"/>
+      <c r="D5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
@@ -1336,28 +1371,28 @@
       <c r="E6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="17">
-        <v>1</v>
-      </c>
-      <c r="G7" s="18"/>
+      <c r="F7" s="9">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2"/>
@@ -1371,10 +1406,10 @@
       <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2"/>
@@ -1388,10 +1423,10 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="3"/>
@@ -1405,10 +1440,10 @@
       <c r="F10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="3"/>
@@ -1422,10 +1457,10 @@
       <c r="F11" s="3">
         <v>1</v>
       </c>
-      <c r="G11" s="22"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="3"/>
@@ -1439,10 +1474,10 @@
       <c r="F12" s="3">
         <v>1</v>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="3"/>
@@ -1456,10 +1491,10 @@
       <c r="F13" s="3">
         <v>1</v>
       </c>
-      <c r="G13" s="22"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1477,10 +1512,10 @@
       <c r="F14" s="3">
         <v>1</v>
       </c>
-      <c r="G14" s="22"/>
+      <c r="G14" s="14"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="3"/>
@@ -1494,10 +1529,10 @@
       <c r="F15" s="3">
         <v>1</v>
       </c>
-      <c r="G15" s="22"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="3"/>
@@ -1511,10 +1546,10 @@
       <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="3"/>
@@ -1528,10 +1563,10 @@
       <c r="F17" s="3">
         <v>1</v>
       </c>
-      <c r="G17" s="22"/>
+      <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="3"/>
@@ -1545,10 +1580,10 @@
       <c r="F18" s="3">
         <v>1</v>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="3"/>
@@ -1562,10 +1597,10 @@
       <c r="F19" s="3">
         <v>1</v>
       </c>
-      <c r="G19" s="22"/>
+      <c r="G19" s="14"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="3"/>
@@ -1579,10 +1614,10 @@
       <c r="F20" s="3">
         <v>1</v>
       </c>
-      <c r="G20" s="22"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="3"/>
@@ -1596,10 +1631,10 @@
       <c r="F21" s="3">
         <v>1</v>
       </c>
-      <c r="G21" s="22"/>
+      <c r="G21" s="14"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1617,10 +1652,10 @@
       <c r="F22" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G22" s="22"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="3"/>
@@ -1634,10 +1669,10 @@
       <c r="F23" s="3">
         <v>1</v>
       </c>
-      <c r="G23" s="22"/>
+      <c r="G23" s="14"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="3"/>
@@ -1651,10 +1686,10 @@
       <c r="F24" s="3">
         <v>1</v>
       </c>
-      <c r="G24" s="22"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="3"/>
@@ -1668,10 +1703,10 @@
       <c r="F25" s="3">
         <v>1</v>
       </c>
-      <c r="G25" s="22"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B26" s="3"/>
@@ -1685,10 +1720,10 @@
       <c r="F26" s="3">
         <v>1</v>
       </c>
-      <c r="G26" s="22"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="3"/>
@@ -1702,10 +1737,10 @@
       <c r="F27" s="3">
         <v>1</v>
       </c>
-      <c r="G27" s="22"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="3"/>
@@ -1719,10 +1754,10 @@
       <c r="F28" s="3">
         <v>1</v>
       </c>
-      <c r="G28" s="22"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -1740,10 +1775,10 @@
       <c r="F29" s="3">
         <v>1</v>
       </c>
-      <c r="G29" s="22"/>
+      <c r="G29" s="14"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="3"/>
@@ -1757,10 +1792,10 @@
       <c r="F30" s="3">
         <v>1</v>
       </c>
-      <c r="G30" s="22"/>
+      <c r="G30" s="14"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="3"/>
@@ -1774,10 +1809,10 @@
       <c r="F31" s="3">
         <v>1</v>
       </c>
-      <c r="G31" s="22"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B32" s="3"/>
@@ -1791,10 +1826,10 @@
       <c r="F32" s="3">
         <v>1</v>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="3"/>
@@ -1808,10 +1843,10 @@
       <c r="F33" s="3">
         <v>1</v>
       </c>
-      <c r="G33" s="22"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="3"/>
@@ -1825,10 +1860,10 @@
       <c r="F34" s="3">
         <v>1</v>
       </c>
-      <c r="G34" s="22"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B35" s="3"/>
@@ -1842,10 +1877,10 @@
       <c r="F35" s="3">
         <v>1</v>
       </c>
-      <c r="G35" s="22"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="3"/>
@@ -1859,10 +1894,10 @@
       <c r="F36" s="3">
         <v>1</v>
       </c>
-      <c r="G36" s="22"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="3"/>
@@ -1876,10 +1911,10 @@
       <c r="F37" s="3">
         <v>1</v>
       </c>
-      <c r="G37" s="22"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="3"/>
@@ -1893,10 +1928,10 @@
       <c r="F38" s="3">
         <v>1</v>
       </c>
-      <c r="G38" s="22"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B39" s="3"/>
@@ -1910,10 +1945,10 @@
       <c r="F39" s="3">
         <v>1</v>
       </c>
-      <c r="G39" s="22"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B40" s="3"/>
@@ -1927,10 +1962,10 @@
       <c r="F40" s="3">
         <v>1</v>
       </c>
-      <c r="G40" s="22"/>
+      <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="3"/>
@@ -1944,10 +1979,10 @@
       <c r="F41" s="3">
         <v>1</v>
       </c>
-      <c r="G41" s="22"/>
+      <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B42" s="3"/>
@@ -1961,10 +1996,10 @@
       <c r="F42" s="3">
         <v>1</v>
       </c>
-      <c r="G42" s="22"/>
+      <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B43" s="3"/>
@@ -1978,10 +2013,10 @@
       <c r="F43" s="3">
         <v>1</v>
       </c>
-      <c r="G43" s="22"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B44" s="3"/>
@@ -1995,10 +2030,10 @@
       <c r="F44" s="3">
         <v>1</v>
       </c>
-      <c r="G44" s="22"/>
+      <c r="G44" s="14"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B45" s="3"/>
@@ -2012,10 +2047,10 @@
       <c r="F45" s="3">
         <v>1</v>
       </c>
-      <c r="G45" s="22"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -2033,10 +2068,10 @@
       <c r="F46" s="3">
         <v>1</v>
       </c>
-      <c r="G46" s="22"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3"/>
@@ -2050,10 +2085,10 @@
       <c r="F47" s="3">
         <v>1</v>
       </c>
-      <c r="G47" s="22"/>
+      <c r="G47" s="14"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="3"/>
@@ -2067,10 +2102,10 @@
       <c r="F48" s="3">
         <v>1</v>
       </c>
-      <c r="G48" s="22"/>
+      <c r="G48" s="14"/>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="3"/>
@@ -2084,10 +2119,10 @@
       <c r="F49" s="3">
         <v>1</v>
       </c>
-      <c r="G49" s="22"/>
+      <c r="G49" s="14"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B50" s="3"/>
@@ -2101,10 +2136,10 @@
       <c r="F50" s="3">
         <v>1</v>
       </c>
-      <c r="G50" s="22"/>
+      <c r="G50" s="14"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B51" s="3"/>
@@ -2118,10 +2153,10 @@
       <c r="F51" s="3">
         <v>1</v>
       </c>
-      <c r="G51" s="22"/>
+      <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B52" s="3"/>
@@ -2135,10 +2170,10 @@
       <c r="F52" s="3">
         <v>1</v>
       </c>
-      <c r="G52" s="22"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B53" s="3"/>
@@ -2152,10 +2187,10 @@
       <c r="F53" s="3">
         <v>1</v>
       </c>
-      <c r="G53" s="22"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="3"/>
@@ -2169,10 +2204,10 @@
       <c r="F54" s="3">
         <v>1</v>
       </c>
-      <c r="G54" s="22"/>
+      <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B55" s="3"/>
@@ -2186,10 +2221,10 @@
       <c r="F55" s="3">
         <v>1</v>
       </c>
-      <c r="G55" s="22"/>
+      <c r="G55" s="14"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="3"/>
@@ -2203,10 +2238,10 @@
       <c r="F56" s="3">
         <v>1</v>
       </c>
-      <c r="G56" s="22"/>
+      <c r="G56" s="14"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B57" s="3"/>
@@ -2220,10 +2255,10 @@
       <c r="F57" s="3">
         <v>1</v>
       </c>
-      <c r="G57" s="22"/>
+      <c r="G57" s="14"/>
     </row>
     <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B58" s="3"/>
@@ -2237,10 +2272,10 @@
       <c r="F58" s="3">
         <v>1</v>
       </c>
-      <c r="G58" s="22"/>
+      <c r="G58" s="14"/>
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B59" s="3"/>
@@ -2254,10 +2289,10 @@
       <c r="F59" s="3">
         <v>1</v>
       </c>
-      <c r="G59" s="22"/>
+      <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B60" s="3"/>
@@ -2271,10 +2306,10 @@
       <c r="F60" s="3">
         <v>1</v>
       </c>
-      <c r="G60" s="22"/>
+      <c r="G60" s="14"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
+      <c r="A61" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B61" s="3"/>
@@ -2288,10 +2323,10 @@
       <c r="F61" s="3">
         <v>1</v>
       </c>
-      <c r="G61" s="22"/>
+      <c r="G61" s="14"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B62" s="3"/>
@@ -2305,10 +2340,10 @@
       <c r="F62" s="3">
         <v>1</v>
       </c>
-      <c r="G62" s="22"/>
+      <c r="G62" s="14"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
+      <c r="A63" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B63" s="3"/>
@@ -2322,10 +2357,10 @@
       <c r="F63" s="3">
         <v>1</v>
       </c>
-      <c r="G63" s="22"/>
+      <c r="G63" s="14"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B64" s="3"/>
@@ -2339,10 +2374,10 @@
       <c r="F64" s="3">
         <v>1</v>
       </c>
-      <c r="G64" s="22"/>
+      <c r="G64" s="14"/>
     </row>
     <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="21" t="s">
+      <c r="A65" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B65" s="3"/>
@@ -2356,10 +2391,10 @@
       <c r="F65" s="3">
         <v>1</v>
       </c>
-      <c r="G65" s="22"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B66" s="3"/>
@@ -2373,10 +2408,10 @@
       <c r="F66" s="3">
         <v>1</v>
       </c>
-      <c r="G66" s="22"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="21" t="s">
+      <c r="A67" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B67" s="3"/>
@@ -2390,10 +2425,10 @@
       <c r="F67" s="3">
         <v>1</v>
       </c>
-      <c r="G67" s="22"/>
+      <c r="G67" s="14"/>
     </row>
     <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B68" s="3"/>
@@ -2407,10 +2442,10 @@
       <c r="F68" s="3">
         <v>1</v>
       </c>
-      <c r="G68" s="22"/>
+      <c r="G68" s="14"/>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="21" t="s">
+      <c r="A69" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B69" s="3"/>
@@ -2424,10 +2459,10 @@
       <c r="F69" s="3">
         <v>1</v>
       </c>
-      <c r="G69" s="22"/>
+      <c r="G69" s="14"/>
     </row>
     <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B70" s="3"/>
@@ -2441,10 +2476,10 @@
       <c r="F70" s="3">
         <v>1</v>
       </c>
-      <c r="G70" s="22"/>
+      <c r="G70" s="14"/>
     </row>
     <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="21" t="s">
+      <c r="A71" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B71" s="3"/>
@@ -2458,10 +2493,10 @@
       <c r="F71" s="3">
         <v>1</v>
       </c>
-      <c r="G71" s="22"/>
+      <c r="G71" s="14"/>
     </row>
     <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B72" s="3"/>
@@ -2475,10 +2510,10 @@
       <c r="F72" s="3">
         <v>1</v>
       </c>
-      <c r="G72" s="22"/>
+      <c r="G72" s="14"/>
     </row>
     <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="21" t="s">
+      <c r="A73" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B73" s="3"/>
@@ -2492,10 +2527,10 @@
       <c r="F73" s="3">
         <v>1</v>
       </c>
-      <c r="G73" s="22"/>
+      <c r="G73" s="14"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B74" s="3"/>
@@ -2509,10 +2544,10 @@
       <c r="F74" s="3">
         <v>1</v>
       </c>
-      <c r="G74" s="22"/>
+      <c r="G74" s="14"/>
     </row>
     <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B75" s="3"/>
@@ -2526,10 +2561,10 @@
       <c r="F75" s="3">
         <v>1</v>
       </c>
-      <c r="G75" s="22"/>
+      <c r="G75" s="14"/>
     </row>
     <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B76" s="3"/>
@@ -2543,10 +2578,10 @@
       <c r="F76" s="3">
         <v>1</v>
       </c>
-      <c r="G76" s="22"/>
+      <c r="G76" s="14"/>
     </row>
     <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="21" t="s">
+      <c r="A77" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B77" s="3"/>
@@ -2560,10 +2595,10 @@
       <c r="F77" s="3">
         <v>1</v>
       </c>
-      <c r="G77" s="22"/>
+      <c r="G77" s="14"/>
     </row>
     <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B78" s="3"/>
@@ -2577,10 +2612,10 @@
       <c r="F78" s="3">
         <v>1</v>
       </c>
-      <c r="G78" s="22"/>
+      <c r="G78" s="14"/>
     </row>
     <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="21" t="s">
+      <c r="A79" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B79" s="3"/>
@@ -2594,10 +2629,10 @@
       <c r="F79" s="3">
         <v>1</v>
       </c>
-      <c r="G79" s="22"/>
+      <c r="G79" s="14"/>
     </row>
     <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B80" s="3"/>
@@ -2611,10 +2646,10 @@
       <c r="F80" s="3">
         <v>1</v>
       </c>
-      <c r="G80" s="22"/>
+      <c r="G80" s="14"/>
     </row>
     <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="21" t="s">
+      <c r="A81" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B81" s="3"/>
@@ -2628,10 +2663,10 @@
       <c r="F81" s="3">
         <v>1</v>
       </c>
-      <c r="G81" s="22"/>
+      <c r="G81" s="14"/>
     </row>
     <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B82" s="3"/>
@@ -2645,10 +2680,10 @@
       <c r="F82" s="3">
         <v>1</v>
       </c>
-      <c r="G82" s="22"/>
+      <c r="G82" s="14"/>
     </row>
     <row r="83" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="21" t="s">
+      <c r="A83" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B83" s="3"/>
@@ -2662,10 +2697,10 @@
       <c r="F83" s="3">
         <v>1</v>
       </c>
-      <c r="G83" s="22"/>
+      <c r="G83" s="14"/>
     </row>
     <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="21" t="s">
+      <c r="A84" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B84" s="3"/>
@@ -2679,10 +2714,10 @@
       <c r="F84" s="3">
         <v>1</v>
       </c>
-      <c r="G84" s="22"/>
+      <c r="G84" s="14"/>
     </row>
     <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="21" t="s">
+      <c r="A85" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B85" s="3"/>
@@ -2696,10 +2731,10 @@
       <c r="F85" s="3">
         <v>1</v>
       </c>
-      <c r="G85" s="22"/>
+      <c r="G85" s="14"/>
     </row>
     <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="21" t="s">
+      <c r="A86" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B86" s="3"/>
@@ -2713,10 +2748,10 @@
       <c r="F86" s="3">
         <v>1</v>
       </c>
-      <c r="G86" s="22"/>
+      <c r="G86" s="14"/>
     </row>
     <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="21" t="s">
+      <c r="A87" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B87" s="3"/>
@@ -2730,10 +2765,10 @@
       <c r="F87" s="3">
         <v>1</v>
       </c>
-      <c r="G87" s="22"/>
+      <c r="G87" s="14"/>
     </row>
     <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="21" t="s">
+      <c r="A88" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B88" s="3"/>
@@ -2747,10 +2782,10 @@
       <c r="F88" s="3">
         <v>1</v>
       </c>
-      <c r="G88" s="22"/>
+      <c r="G88" s="14"/>
     </row>
     <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="21" t="s">
+      <c r="A89" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B89" s="3"/>
@@ -2764,10 +2799,10 @@
       <c r="F89" s="3">
         <v>1</v>
       </c>
-      <c r="G89" s="22"/>
+      <c r="G89" s="14"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B90" s="3"/>
@@ -2781,10 +2816,10 @@
       <c r="F90" s="3">
         <v>1</v>
       </c>
-      <c r="G90" s="22"/>
+      <c r="G90" s="14"/>
     </row>
     <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="21" t="s">
+      <c r="A91" s="13" t="s">
         <v>94</v>
       </c>
       <c r="B91" s="3"/>
@@ -2798,10 +2833,10 @@
       <c r="F91" s="3">
         <v>1</v>
       </c>
-      <c r="G91" s="22"/>
+      <c r="G91" s="14"/>
     </row>
     <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="21" t="s">
+      <c r="A92" s="13" t="s">
         <v>94</v>
       </c>
       <c r="B92" s="3"/>
@@ -2815,10 +2850,10 @@
       <c r="F92" s="3">
         <v>1</v>
       </c>
-      <c r="G92" s="22"/>
+      <c r="G92" s="14"/>
     </row>
     <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="21" t="s">
+      <c r="A93" s="13" t="s">
         <v>94</v>
       </c>
       <c r="B93" s="3"/>
@@ -2832,10 +2867,10 @@
       <c r="F93" s="3">
         <v>1</v>
       </c>
-      <c r="G93" s="22"/>
+      <c r="G93" s="14"/>
     </row>
     <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="13" t="s">
         <v>94</v>
       </c>
       <c r="B94" s="3"/>
@@ -2849,10 +2884,10 @@
       <c r="F94" s="3">
         <v>1</v>
       </c>
-      <c r="G94" s="22"/>
+      <c r="G94" s="14"/>
     </row>
     <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="21" t="s">
+      <c r="A95" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B95" s="3"/>
@@ -2866,10 +2901,10 @@
       <c r="F95" s="3">
         <v>1</v>
       </c>
-      <c r="G95" s="22"/>
+      <c r="G95" s="14"/>
     </row>
     <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="21" t="s">
+      <c r="A96" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B96" s="3"/>
@@ -2883,10 +2918,10 @@
       <c r="F96" s="3">
         <v>1</v>
       </c>
-      <c r="G96" s="22"/>
+      <c r="G96" s="14"/>
     </row>
     <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="21" t="s">
+      <c r="A97" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B97" s="3"/>
@@ -2900,10 +2935,10 @@
       <c r="F97" s="3">
         <v>1</v>
       </c>
-      <c r="G97" s="22"/>
+      <c r="G97" s="14"/>
     </row>
     <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="21" t="s">
+      <c r="A98" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B98" s="3"/>
@@ -2917,10 +2952,10 @@
       <c r="F98" s="3">
         <v>1</v>
       </c>
-      <c r="G98" s="22"/>
+      <c r="G98" s="14"/>
     </row>
     <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="21" t="s">
+      <c r="A99" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B99" s="3"/>
@@ -2934,10 +2969,10 @@
       <c r="F99" s="3">
         <v>1</v>
       </c>
-      <c r="G99" s="22"/>
+      <c r="G99" s="14"/>
     </row>
     <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="21" t="s">
+      <c r="A100" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B100" s="3"/>
@@ -2951,10 +2986,10 @@
       <c r="F100" s="3">
         <v>1</v>
       </c>
-      <c r="G100" s="22"/>
+      <c r="G100" s="14"/>
     </row>
     <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="21" t="s">
+      <c r="A101" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B101" s="3"/>
@@ -2968,10 +3003,10 @@
       <c r="F101" s="3">
         <v>1</v>
       </c>
-      <c r="G101" s="22"/>
+      <c r="G101" s="14"/>
     </row>
     <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="21" t="s">
+      <c r="A102" s="13" t="s">
         <v>109</v>
       </c>
       <c r="B102" s="3"/>
@@ -2985,10 +3020,10 @@
       <c r="F102" s="3">
         <v>1</v>
       </c>
-      <c r="G102" s="22"/>
+      <c r="G102" s="14"/>
     </row>
     <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="21" t="s">
+      <c r="A103" s="13" t="s">
         <v>109</v>
       </c>
       <c r="B103" s="3"/>
@@ -3002,10 +3037,10 @@
       <c r="F103" s="3">
         <v>1</v>
       </c>
-      <c r="G103" s="22"/>
+      <c r="G103" s="14"/>
     </row>
     <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="21" t="s">
+      <c r="A104" s="13" t="s">
         <v>109</v>
       </c>
       <c r="B104" s="3"/>
@@ -3019,10 +3054,10 @@
       <c r="F104" s="3">
         <v>1</v>
       </c>
-      <c r="G104" s="22"/>
+      <c r="G104" s="14"/>
     </row>
     <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="21" t="s">
+      <c r="A105" s="13" t="s">
         <v>109</v>
       </c>
       <c r="B105" s="3"/>
@@ -3036,10 +3071,10 @@
       <c r="F105" s="3">
         <v>1</v>
       </c>
-      <c r="G105" s="22"/>
+      <c r="G105" s="14"/>
     </row>
     <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="13" t="s">
         <v>114</v>
       </c>
       <c r="B106" s="3"/>
@@ -3053,10 +3088,10 @@
       <c r="F106" s="3">
         <v>1</v>
       </c>
-      <c r="G106" s="22"/>
+      <c r="G106" s="14"/>
     </row>
     <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="21" t="s">
+      <c r="A107" s="13" t="s">
         <v>114</v>
       </c>
       <c r="B107" s="3"/>
@@ -3070,10 +3105,10 @@
       <c r="F107" s="3">
         <v>1</v>
       </c>
-      <c r="G107" s="22"/>
+      <c r="G107" s="14"/>
     </row>
     <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="21" t="s">
+      <c r="A108" s="13" t="s">
         <v>118</v>
       </c>
       <c r="B108" s="3"/>
@@ -3087,10 +3122,10 @@
       <c r="F108" s="3">
         <v>1</v>
       </c>
-      <c r="G108" s="22"/>
+      <c r="G108" s="14"/>
     </row>
     <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="21" t="s">
+      <c r="A109" s="13" t="s">
         <v>118</v>
       </c>
       <c r="B109" s="3"/>
@@ -3104,10 +3139,10 @@
       <c r="F109" s="3">
         <v>1</v>
       </c>
-      <c r="G109" s="22"/>
+      <c r="G109" s="14"/>
     </row>
     <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="21" t="s">
+      <c r="A110" s="13" t="s">
         <v>120</v>
       </c>
       <c r="B110" s="3"/>
@@ -3121,10 +3156,10 @@
       <c r="F110" s="3">
         <v>1</v>
       </c>
-      <c r="G110" s="22"/>
+      <c r="G110" s="14"/>
     </row>
     <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="21" t="s">
+      <c r="A111" s="13" t="s">
         <v>120</v>
       </c>
       <c r="B111" s="3"/>
@@ -3138,10 +3173,10 @@
       <c r="F111" s="3">
         <v>1</v>
       </c>
-      <c r="G111" s="22"/>
+      <c r="G111" s="14"/>
     </row>
     <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="13" t="s">
         <v>120</v>
       </c>
       <c r="B112" s="3"/>
@@ -3155,10 +3190,10 @@
       <c r="F112" s="3">
         <v>1</v>
       </c>
-      <c r="G112" s="22"/>
+      <c r="G112" s="14"/>
     </row>
     <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="21" t="s">
+      <c r="A113" s="13" t="s">
         <v>121</v>
       </c>
       <c r="B113" s="3"/>
@@ -3172,10 +3207,10 @@
       <c r="F113" s="3">
         <v>1</v>
       </c>
-      <c r="G113" s="22"/>
+      <c r="G113" s="14"/>
     </row>
     <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="21" t="s">
+      <c r="A114" s="13" t="s">
         <v>121</v>
       </c>
       <c r="B114" s="3"/>
@@ -3189,10 +3224,10 @@
       <c r="F114" s="3">
         <v>1</v>
       </c>
-      <c r="G114" s="22"/>
+      <c r="G114" s="14"/>
     </row>
     <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="21" t="s">
+      <c r="A115" s="13" t="s">
         <v>121</v>
       </c>
       <c r="B115" s="3"/>
@@ -3206,10 +3241,10 @@
       <c r="F115" s="3">
         <v>1</v>
       </c>
-      <c r="G115" s="22"/>
+      <c r="G115" s="14"/>
     </row>
     <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="13" t="s">
         <v>121</v>
       </c>
       <c r="B116" s="3"/>
@@ -3223,10 +3258,10 @@
       <c r="F116" s="3">
         <v>1</v>
       </c>
-      <c r="G116" s="22"/>
+      <c r="G116" s="14"/>
     </row>
     <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B117" s="3"/>
@@ -3240,10 +3275,10 @@
       <c r="F117" s="3">
         <v>1</v>
       </c>
-      <c r="G117" s="22"/>
+      <c r="G117" s="14"/>
     </row>
     <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="21" t="s">
+      <c r="A118" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B118" s="3"/>
@@ -3257,10 +3292,10 @@
       <c r="F118" s="3">
         <v>1</v>
       </c>
-      <c r="G118" s="22"/>
+      <c r="G118" s="14"/>
     </row>
     <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="21" t="s">
+      <c r="A119" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B119" s="3"/>
@@ -3274,10 +3309,10 @@
       <c r="F119" s="3">
         <v>1</v>
       </c>
-      <c r="G119" s="22"/>
+      <c r="G119" s="14"/>
     </row>
     <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B120" s="3"/>
@@ -3291,10 +3326,10 @@
       <c r="F120" s="3">
         <v>1</v>
       </c>
-      <c r="G120" s="22"/>
+      <c r="G120" s="14"/>
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="21" t="s">
+      <c r="A121" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B121" s="3"/>
@@ -3308,10 +3343,10 @@
       <c r="F121" s="3">
         <v>1</v>
       </c>
-      <c r="G121" s="22"/>
+      <c r="G121" s="14"/>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B122" s="3"/>
@@ -3325,10 +3360,10 @@
       <c r="F122" s="3">
         <v>1</v>
       </c>
-      <c r="G122" s="22"/>
+      <c r="G122" s="14"/>
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B123" s="3"/>
@@ -3342,10 +3377,10 @@
       <c r="F123" s="3">
         <v>1</v>
       </c>
-      <c r="G123" s="22"/>
+      <c r="G123" s="14"/>
     </row>
     <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B124" s="3"/>
@@ -3359,10 +3394,10 @@
       <c r="F124" s="3">
         <v>1</v>
       </c>
-      <c r="G124" s="22"/>
+      <c r="G124" s="14"/>
     </row>
     <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="13" t="s">
         <v>132</v>
       </c>
       <c r="B125" s="3"/>
@@ -3376,10 +3411,10 @@
       <c r="F125" s="3">
         <v>1</v>
       </c>
-      <c r="G125" s="22"/>
+      <c r="G125" s="14"/>
     </row>
     <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="13" t="s">
         <v>132</v>
       </c>
       <c r="B126" s="3"/>
@@ -3393,10 +3428,10 @@
       <c r="F126" s="3">
         <v>1</v>
       </c>
-      <c r="G126" s="22"/>
+      <c r="G126" s="14"/>
     </row>
     <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="21" t="s">
+      <c r="A127" s="13" t="s">
         <v>132</v>
       </c>
       <c r="B127" s="3"/>
@@ -3410,10 +3445,10 @@
       <c r="F127" s="3">
         <v>1</v>
       </c>
-      <c r="G127" s="22"/>
+      <c r="G127" s="14"/>
     </row>
     <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="13" t="s">
         <v>132</v>
       </c>
       <c r="B128" s="3"/>
@@ -3427,10 +3462,10 @@
       <c r="F128" s="3">
         <v>1</v>
       </c>
-      <c r="G128" s="22"/>
+      <c r="G128" s="14"/>
     </row>
     <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="21" t="s">
+      <c r="A129" s="13" t="s">
         <v>133</v>
       </c>
       <c r="B129" s="3"/>
@@ -3444,10 +3479,10 @@
       <c r="F129" s="3">
         <v>1</v>
       </c>
-      <c r="G129" s="22"/>
+      <c r="G129" s="14"/>
     </row>
     <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="13" t="s">
         <v>133</v>
       </c>
       <c r="B130" s="3"/>
@@ -3461,10 +3496,10 @@
       <c r="F130" s="3">
         <v>1</v>
       </c>
-      <c r="G130" s="22"/>
+      <c r="G130" s="14"/>
     </row>
     <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="21" t="s">
+      <c r="A131" s="13" t="s">
         <v>133</v>
       </c>
       <c r="B131" s="3"/>
@@ -3478,10 +3513,10 @@
       <c r="F131" s="3">
         <v>1</v>
       </c>
-      <c r="G131" s="22"/>
+      <c r="G131" s="14"/>
     </row>
     <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B132" s="3"/>
@@ -3495,10 +3530,10 @@
       <c r="F132" s="3">
         <v>1</v>
       </c>
-      <c r="G132" s="22"/>
+      <c r="G132" s="14"/>
     </row>
     <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B133" s="3"/>
@@ -3512,10 +3547,10 @@
       <c r="F133" s="3">
         <v>1</v>
       </c>
-      <c r="G133" s="22"/>
+      <c r="G133" s="14"/>
     </row>
     <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B134" s="3"/>
@@ -3529,10 +3564,10 @@
       <c r="F134" s="3">
         <v>1</v>
       </c>
-      <c r="G134" s="22"/>
+      <c r="G134" s="14"/>
     </row>
     <row r="135" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="21" t="s">
+      <c r="A135" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B135" s="3"/>
@@ -3546,10 +3581,10 @@
       <c r="F135" s="3">
         <v>1</v>
       </c>
-      <c r="G135" s="22"/>
+      <c r="G135" s="14"/>
     </row>
     <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="21" t="s">
+      <c r="A136" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B136" s="3"/>
@@ -3563,10 +3598,10 @@
       <c r="F136" s="3">
         <v>1</v>
       </c>
-      <c r="G136" s="22"/>
+      <c r="G136" s="14"/>
     </row>
     <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="21" t="s">
+      <c r="A137" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B137" s="3"/>
@@ -3580,10 +3615,10 @@
       <c r="F137" s="3">
         <v>1</v>
       </c>
-      <c r="G137" s="22"/>
+      <c r="G137" s="14"/>
     </row>
     <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="21" t="s">
+      <c r="A138" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B138" s="3"/>
@@ -3597,10 +3632,10 @@
       <c r="F138" s="3">
         <v>1</v>
       </c>
-      <c r="G138" s="22"/>
+      <c r="G138" s="14"/>
     </row>
     <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="21" t="s">
+      <c r="A139" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B139" s="3"/>
@@ -3614,10 +3649,10 @@
       <c r="F139" s="3">
         <v>1</v>
       </c>
-      <c r="G139" s="22"/>
+      <c r="G139" s="14"/>
     </row>
     <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="21" t="s">
+      <c r="A140" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B140" s="3"/>
@@ -3631,10 +3666,10 @@
       <c r="F140" s="3">
         <v>1</v>
       </c>
-      <c r="G140" s="22"/>
+      <c r="G140" s="14"/>
     </row>
     <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="21" t="s">
+      <c r="A141" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B141" s="3" t="s">
@@ -3652,10 +3687,10 @@
       <c r="F141" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G141" s="22"/>
+      <c r="G141" s="14"/>
     </row>
     <row r="142" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="21" t="s">
+      <c r="A142" s="13" t="s">
         <v>147</v>
       </c>
       <c r="B142" s="3"/>
@@ -3669,10 +3704,10 @@
       <c r="F142" s="3">
         <v>1</v>
       </c>
-      <c r="G142" s="22"/>
+      <c r="G142" s="14"/>
     </row>
     <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="21" t="s">
+      <c r="A143" s="13" t="s">
         <v>147</v>
       </c>
       <c r="B143" s="3"/>
@@ -3686,10 +3721,10 @@
       <c r="F143" s="3">
         <v>1</v>
       </c>
-      <c r="G143" s="22"/>
+      <c r="G143" s="14"/>
     </row>
     <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="21" t="s">
+      <c r="A144" s="13" t="s">
         <v>147</v>
       </c>
       <c r="B144" s="3"/>
@@ -3703,10 +3738,10 @@
       <c r="F144" s="3">
         <v>1</v>
       </c>
-      <c r="G144" s="22"/>
+      <c r="G144" s="14"/>
     </row>
     <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B145" s="3"/>
@@ -3720,10 +3755,10 @@
       <c r="F145" s="3">
         <v>1</v>
       </c>
-      <c r="G145" s="22"/>
+      <c r="G145" s="14"/>
     </row>
     <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="21" t="s">
+      <c r="A146" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B146" s="3"/>
@@ -3737,10 +3772,10 @@
       <c r="F146" s="3">
         <v>1</v>
       </c>
-      <c r="G146" s="22"/>
+      <c r="G146" s="14"/>
     </row>
     <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="21" t="s">
+      <c r="A147" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B147" s="3"/>
@@ -3754,10 +3789,10 @@
       <c r="F147" s="3">
         <v>1</v>
       </c>
-      <c r="G147" s="22"/>
+      <c r="G147" s="14"/>
     </row>
     <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="21" t="s">
+      <c r="A148" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B148" s="3" t="s">
@@ -3775,10 +3810,10 @@
       <c r="F148" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G148" s="22"/>
+      <c r="G148" s="14"/>
     </row>
     <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="21" t="s">
+      <c r="A149" s="13" t="s">
         <v>152</v>
       </c>
       <c r="B149" s="3"/>
@@ -3792,10 +3827,10 @@
       <c r="F149" s="3">
         <v>1</v>
       </c>
-      <c r="G149" s="22"/>
+      <c r="G149" s="14"/>
     </row>
     <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="21" t="s">
+      <c r="A150" s="13" t="s">
         <v>152</v>
       </c>
       <c r="B150" s="3"/>
@@ -3809,10 +3844,10 @@
       <c r="F150" s="3">
         <v>1</v>
       </c>
-      <c r="G150" s="22"/>
+      <c r="G150" s="14"/>
     </row>
     <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="21" t="s">
+      <c r="A151" s="13" t="s">
         <v>153</v>
       </c>
       <c r="B151" s="3"/>
@@ -3826,10 +3861,10 @@
       <c r="F151" s="3">
         <v>1</v>
       </c>
-      <c r="G151" s="22"/>
+      <c r="G151" s="14"/>
     </row>
     <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="21" t="s">
+      <c r="A152" s="13" t="s">
         <v>153</v>
       </c>
       <c r="B152" s="3"/>
@@ -3843,10 +3878,10 @@
       <c r="F152" s="3">
         <v>1</v>
       </c>
-      <c r="G152" s="22"/>
+      <c r="G152" s="14"/>
     </row>
     <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="21" t="s">
+      <c r="A153" s="13" t="s">
         <v>153</v>
       </c>
       <c r="B153" s="3"/>
@@ -3860,10 +3895,10 @@
       <c r="F153" s="3">
         <v>1</v>
       </c>
-      <c r="G153" s="22"/>
+      <c r="G153" s="14"/>
     </row>
     <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="13" t="s">
         <v>154</v>
       </c>
       <c r="B154" s="3"/>
@@ -3877,10 +3912,10 @@
       <c r="F154" s="3">
         <v>1</v>
       </c>
-      <c r="G154" s="22"/>
+      <c r="G154" s="14"/>
     </row>
     <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="21" t="s">
+      <c r="A155" s="13" t="s">
         <v>154</v>
       </c>
       <c r="B155" s="3"/>
@@ -3894,10 +3929,10 @@
       <c r="F155" s="3">
         <v>1</v>
       </c>
-      <c r="G155" s="22"/>
+      <c r="G155" s="14"/>
     </row>
     <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="13" t="s">
         <v>154</v>
       </c>
       <c r="B156" s="3"/>
@@ -3911,10 +3946,10 @@
       <c r="F156" s="3">
         <v>1</v>
       </c>
-      <c r="G156" s="22"/>
+      <c r="G156" s="14"/>
     </row>
     <row r="157" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="21" t="s">
+      <c r="A157" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B157" s="3"/>
@@ -3928,10 +3963,10 @@
       <c r="F157" s="3">
         <v>1</v>
       </c>
-      <c r="G157" s="22"/>
+      <c r="G157" s="14"/>
     </row>
     <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="21" t="s">
+      <c r="A158" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B158" s="3"/>
@@ -3945,10 +3980,10 @@
       <c r="F158" s="3">
         <v>1</v>
       </c>
-      <c r="G158" s="22"/>
+      <c r="G158" s="14"/>
     </row>
     <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="21" t="s">
+      <c r="A159" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B159" s="3"/>
@@ -3962,10 +3997,10 @@
       <c r="F159" s="3">
         <v>1</v>
       </c>
-      <c r="G159" s="22"/>
+      <c r="G159" s="14"/>
     </row>
     <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="21" t="s">
+      <c r="A160" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B160" s="3"/>
@@ -3979,10 +4014,10 @@
       <c r="F160" s="3">
         <v>1</v>
       </c>
-      <c r="G160" s="22"/>
+      <c r="G160" s="14"/>
     </row>
     <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="21" t="s">
+      <c r="A161" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B161" s="3"/>
@@ -3996,10 +4031,10 @@
       <c r="F161" s="3">
         <v>1</v>
       </c>
-      <c r="G161" s="22"/>
+      <c r="G161" s="14"/>
     </row>
     <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="21" t="s">
+      <c r="A162" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B162" s="3"/>
@@ -4013,10 +4048,10 @@
       <c r="F162" s="3">
         <v>1</v>
       </c>
-      <c r="G162" s="22"/>
+      <c r="G162" s="14"/>
     </row>
     <row r="163" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="21" t="s">
+      <c r="A163" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B163" s="3"/>
@@ -4030,10 +4065,10 @@
       <c r="F163" s="3">
         <v>1</v>
       </c>
-      <c r="G163" s="22"/>
+      <c r="G163" s="14"/>
     </row>
     <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="21" t="s">
+      <c r="A164" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B164" s="3"/>
@@ -4047,10 +4082,10 @@
       <c r="F164" s="3">
         <v>1</v>
       </c>
-      <c r="G164" s="22"/>
+      <c r="G164" s="14"/>
     </row>
     <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="21" t="s">
+      <c r="A165" s="13" t="s">
         <v>160</v>
       </c>
       <c r="B165" s="3"/>
@@ -4064,10 +4099,10 @@
       <c r="F165" s="3">
         <v>1</v>
       </c>
-      <c r="G165" s="22"/>
+      <c r="G165" s="14"/>
     </row>
     <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="21" t="s">
+      <c r="A166" s="13" t="s">
         <v>160</v>
       </c>
       <c r="B166" s="3"/>
@@ -4081,10 +4116,10 @@
       <c r="F166" s="3">
         <v>1</v>
       </c>
-      <c r="G166" s="22"/>
+      <c r="G166" s="14"/>
     </row>
     <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="21" t="s">
+      <c r="A167" s="13" t="s">
         <v>160</v>
       </c>
       <c r="B167" s="3"/>
@@ -4098,10 +4133,10 @@
       <c r="F167" s="3">
         <v>1</v>
       </c>
-      <c r="G167" s="22"/>
+      <c r="G167" s="14"/>
     </row>
     <row r="168" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="21" t="s">
+      <c r="A168" s="13" t="s">
         <v>161</v>
       </c>
       <c r="B168" s="3"/>
@@ -4115,10 +4150,10 @@
       <c r="F168" s="3">
         <v>1</v>
       </c>
-      <c r="G168" s="22"/>
+      <c r="G168" s="14"/>
     </row>
     <row r="169" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="21" t="s">
+      <c r="A169" s="13" t="s">
         <v>161</v>
       </c>
       <c r="B169" s="3"/>
@@ -4132,10 +4167,10 @@
       <c r="F169" s="3">
         <v>1</v>
       </c>
-      <c r="G169" s="22"/>
+      <c r="G169" s="14"/>
     </row>
     <row r="170" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="21" t="s">
+      <c r="A170" s="13" t="s">
         <v>161</v>
       </c>
       <c r="B170" s="3"/>
@@ -4149,10 +4184,10 @@
       <c r="F170" s="3">
         <v>1</v>
       </c>
-      <c r="G170" s="22"/>
+      <c r="G170" s="14"/>
     </row>
     <row r="171" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="21" t="s">
+      <c r="A171" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B171" s="3"/>
@@ -4166,10 +4201,10 @@
       <c r="F171" s="3">
         <v>1</v>
       </c>
-      <c r="G171" s="22"/>
+      <c r="G171" s="14"/>
     </row>
     <row r="172" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="21" t="s">
+      <c r="A172" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B172" s="3"/>
@@ -4183,10 +4218,10 @@
       <c r="F172" s="3">
         <v>1</v>
       </c>
-      <c r="G172" s="22"/>
+      <c r="G172" s="14"/>
     </row>
     <row r="173" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="21" t="s">
+      <c r="A173" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B173" s="3"/>
@@ -4200,10 +4235,10 @@
       <c r="F173" s="3">
         <v>1</v>
       </c>
-      <c r="G173" s="22"/>
+      <c r="G173" s="14"/>
     </row>
     <row r="174" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" s="21" t="s">
+      <c r="A174" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B174" s="3"/>
@@ -4217,10 +4252,10 @@
       <c r="F174" s="3">
         <v>1</v>
       </c>
-      <c r="G174" s="22"/>
+      <c r="G174" s="14"/>
     </row>
     <row r="175" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="21" t="s">
+      <c r="A175" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B175" s="3"/>
@@ -4234,10 +4269,10 @@
       <c r="F175" s="3">
         <v>1</v>
       </c>
-      <c r="G175" s="22"/>
+      <c r="G175" s="14"/>
     </row>
     <row r="176" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="21" t="s">
+      <c r="A176" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B176" s="3" t="s">
@@ -4255,10 +4290,10 @@
       <c r="F176" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G176" s="22"/>
+      <c r="G176" s="14"/>
     </row>
     <row r="177" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="21" t="s">
+      <c r="A177" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B177" s="3"/>
@@ -4272,10 +4307,10 @@
       <c r="F177" s="3">
         <v>1</v>
       </c>
-      <c r="G177" s="22"/>
+      <c r="G177" s="14"/>
     </row>
     <row r="178" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" s="21" t="s">
+      <c r="A178" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B178" s="3"/>
@@ -4289,10 +4324,10 @@
       <c r="F178" s="3">
         <v>1</v>
       </c>
-      <c r="G178" s="22"/>
+      <c r="G178" s="14"/>
     </row>
     <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="21" t="s">
+      <c r="A179" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B179" s="3"/>
@@ -4306,10 +4341,10 @@
       <c r="F179" s="3">
         <v>1</v>
       </c>
-      <c r="G179" s="22"/>
+      <c r="G179" s="14"/>
     </row>
     <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="21" t="s">
+      <c r="A180" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B180" s="3" t="s">
@@ -4327,10 +4362,10 @@
       <c r="F180" s="3">
         <v>1</v>
       </c>
-      <c r="G180" s="22"/>
+      <c r="G180" s="14"/>
     </row>
     <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="21" t="s">
+      <c r="A181" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B181" s="3"/>
@@ -4344,10 +4379,10 @@
       <c r="F181" s="3">
         <v>1</v>
       </c>
-      <c r="G181" s="22"/>
+      <c r="G181" s="14"/>
     </row>
     <row r="182" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="21" t="s">
+      <c r="A182" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B182" s="3"/>
@@ -4361,10 +4396,10 @@
       <c r="F182" s="3">
         <v>1</v>
       </c>
-      <c r="G182" s="22"/>
+      <c r="G182" s="14"/>
     </row>
     <row r="183" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="21" t="s">
+      <c r="A183" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B183" s="3"/>
@@ -4378,10 +4413,10 @@
       <c r="F183" s="3">
         <v>1</v>
       </c>
-      <c r="G183" s="22"/>
+      <c r="G183" s="14"/>
     </row>
     <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="21" t="s">
+      <c r="A184" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B184" s="3"/>
@@ -4395,28 +4430,28 @@
       <c r="F184" s="3">
         <v>1</v>
       </c>
-      <c r="G184" s="22"/>
+      <c r="G184" s="14"/>
     </row>
     <row r="185" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="23" t="s">
+      <c r="A185" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B185" s="24" t="s">
+      <c r="B185" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="C185" s="24" t="s">
+      <c r="C185" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D185" s="24" t="s">
+      <c r="D185" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="E185" s="24" t="s">
+      <c r="E185" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F185" s="24" t="s">
+      <c r="F185" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G185" s="25"/>
+      <c r="G185" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="8">
